--- a/datos_14.tablas-resultados.xlsx
+++ b/datos_14.tablas-resultados.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="H2">
-        <v>0.275</v>
+        <v>0.297</v>
       </c>
       <c r="I2">
         <v>0.211</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="H3">
-        <v>0.08359999999999999</v>
+        <v>0.079</v>
       </c>
       <c r="I3">
         <v>0.24</v>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="H4">
-        <v>0.0314</v>
+        <v>0.0338</v>
       </c>
       <c r="I4">
         <v>0.417</v>
